--- a/public/exports-60-250-with-coowners/65120119.xlsx
+++ b/public/exports-60-250-with-coowners/65120119.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798613</t>
+          <t xml:space="preserve">311798611</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
